--- a/capabilities/economic-research/model.xlsx
+++ b/capabilities/economic-research/model.xlsx
@@ -698,11 +698,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>BLS Occupational Outlook Handbook, Graphic Designers (2024-2034 projections): ~20,000 average annual openings. Note: BLS "openings" bundles growth openings with replacement openings (anyone leaving the occupation, any career stage), not specifically junior hires.</t>
+          <t>BLS Employment Projections, Table 1.10 (2025-35 cycle), Graphic Designers (SOC 27-1024): Occupational openings, annual average = 16,000. Replaces an earlier 20,000 figure from the 2024-2034 cycle, updated 2026-10-10 for vintage consistency with the cross-occupation Figure 2 inputs. Note: BLS openings bundles growth openings with replacement openings (anyone leaving the occupation, any career stage), not specifically junior hires.</t>
         </is>
       </c>
     </row>
@@ -758,11 +758,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Jennifer's professional judgment: annual attrition rate applied to the mid-level stock, after each year's new cohort joins (per the agreed ordering). No occupation-specific source found.</t>
+          <t>BLS Employment Projections, Table 1.10 (2025-35 cycle), Graphic Designers (SOC 27-1024): Total occupational separations rate, annual average = 6.5% (2.2% labor-force exit + 4.4% occupational transfer). Replaces the earlier uniform 0.05 judgment call, updated 2026-10-10 -- no occupation-specific source had been found at the time.</t>
         </is>
       </c>
     </row>
